--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_individual_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_individual_h_4.xlsx
@@ -658,7 +658,7 @@
         <v>0.008439271833561955</v>
       </c>
       <c r="C2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>18896994</v>
+        <v>4453022</v>
       </c>
       <c r="L2" t="n">
-        <v>11454647</v>
+        <v>2539349</v>
       </c>
       <c r="M2" t="n">
-        <v>3006860</v>
+        <v>617753</v>
       </c>
       <c r="N2" t="n">
-        <v>175203</v>
+        <v>29789</v>
       </c>
       <c r="O2" t="n">
-        <v>1768777</v>
+        <v>381958</v>
       </c>
       <c r="P2" t="n">
-        <v>687813</v>
+        <v>155499</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999834299087524</v>
+        <v>0.9999990463256836</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9372583627700806</v>
+        <v>0.8848015069961548</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8661730885505676</v>
+        <v>0.7599801421165466</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8321260213851929</v>
+        <v>0.70171058177948</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6626813411712646</v>
+        <v>0.4365904033184052</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8645066022872925</v>
+        <v>0.7552666664123535</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9100475311279297</v>
+        <v>0.8263399600982666</v>
       </c>
       <c r="X2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>19271788</v>
+        <v>4809709</v>
       </c>
       <c r="AG2" t="n">
-        <v>11873762</v>
+        <v>2974674</v>
       </c>
       <c r="AH2" t="n">
-        <v>3197356</v>
+        <v>799643</v>
       </c>
       <c r="AI2" t="n">
-        <v>235916</v>
+        <v>59000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1836054</v>
+        <v>459265</v>
       </c>
       <c r="AK2" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566228985786438</v>
+        <v>0.956451416015625</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112591743469238</v>
+        <v>0.9113048315048218</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.858102023601532</v>
+        <v>0.8578755855560303</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6624639630317688</v>
+        <v>0.6619618535041809</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020282030105591</v>
+        <v>0.9019733667373657</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314249157905579</v>
+        <v>0.931433379650116</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002023734838753813</v>
       </c>
       <c r="C3" t="n">
-        <v>362</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>18896994</v>
+        <v>4453022</v>
       </c>
       <c r="E3" t="n">
-        <v>1210484</v>
+        <v>561444</v>
       </c>
       <c r="F3" t="n">
-        <v>14440</v>
+        <v>7503</v>
       </c>
       <c r="G3" t="n">
-        <v>2004</v>
+        <v>861</v>
       </c>
       <c r="H3" t="n">
-        <v>643</v>
+        <v>376</v>
       </c>
       <c r="I3" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="J3" t="n">
-        <v>40066069</v>
+        <v>10016616</v>
       </c>
       <c r="K3" t="n">
-        <v>43928437</v>
+        <v>10726601</v>
       </c>
       <c r="L3" t="n">
-        <v>50500866</v>
+        <v>12258726</v>
       </c>
       <c r="M3" t="n">
-        <v>60983916</v>
+        <v>15134409</v>
       </c>
       <c r="N3" t="n">
-        <v>64872829</v>
+        <v>16201967</v>
       </c>
       <c r="O3" t="n">
-        <v>63004867</v>
+        <v>15696454</v>
       </c>
       <c r="P3" t="n">
-        <v>64477222</v>
+        <v>16103575</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9389826059341431</v>
+        <v>0.8864859342575073</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8779021501541138</v>
+        <v>0.7768237590789795</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8065877556800842</v>
+        <v>0.6624050736427307</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4916060864925385</v>
+        <v>0.3339911103248596</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8686169981956482</v>
+        <v>0.7498517632484436</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8895759582519531</v>
+        <v>0.8042525053024292</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>19271788</v>
+        <v>4809709</v>
       </c>
       <c r="Z3" t="n">
-        <v>791602</v>
+        <v>198076</v>
       </c>
       <c r="AA3" t="n">
-        <v>34131</v>
+        <v>8559</v>
       </c>
       <c r="AB3" t="n">
-        <v>27146</v>
+        <v>6810</v>
       </c>
       <c r="AC3" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>40066488</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>44319573</v>
+        <v>11087378</v>
       </c>
       <c r="AG3" t="n">
-        <v>51114353</v>
+        <v>12771195</v>
       </c>
       <c r="AH3" t="n">
-        <v>61061800</v>
+        <v>15264532</v>
       </c>
       <c r="AI3" t="n">
-        <v>64841808</v>
+        <v>16210280</v>
       </c>
       <c r="AJ3" t="n">
-        <v>63082667</v>
+        <v>15770309</v>
       </c>
       <c r="AK3" t="n">
-        <v>64492192</v>
+        <v>16123000</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576059579849243</v>
+        <v>0.9574934840202332</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100238084793091</v>
+        <v>0.909995973110199</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576881885528564</v>
+        <v>0.857442319393158</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.66196209192276</v>
+        <v>0.6615017056465149</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016556143760681</v>
+        <v>0.9016192555427551</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313249588012695</v>
+        <v>0.9312165975570679</v>
       </c>
     </row>
     <row r="4">
@@ -929,127 +929,127 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1196623</v>
+        <v>550268</v>
       </c>
       <c r="E4" t="n">
-        <v>11454647</v>
+        <v>2539349</v>
       </c>
       <c r="F4" t="n">
-        <v>366825</v>
+        <v>161062</v>
       </c>
       <c r="G4" t="n">
-        <v>9230</v>
+        <v>5201</v>
       </c>
       <c r="H4" t="n">
-        <v>19123</v>
+        <v>12072</v>
       </c>
       <c r="I4" t="n">
-        <v>1301</v>
+        <v>935</v>
       </c>
       <c r="J4" t="n">
-        <v>419</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>1264996</v>
+        <v>579770</v>
       </c>
       <c r="L4" t="n">
-        <v>1769785</v>
+        <v>801987</v>
       </c>
       <c r="M4" t="n">
-        <v>606607</v>
+        <v>262600</v>
       </c>
       <c r="N4" t="n">
-        <v>89182</v>
+        <v>38442</v>
       </c>
       <c r="O4" t="n">
-        <v>277219</v>
+        <v>123768</v>
       </c>
       <c r="P4" t="n">
-        <v>67986</v>
+        <v>32679</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999917149543762</v>
+        <v>0.9999995231628418</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9381197094917297</v>
+        <v>0.885642945766449</v>
       </c>
       <c r="S4" t="n">
-        <v>0.871998131275177</v>
+        <v>0.7683096528053284</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8191578388214111</v>
+        <v>0.6814915537834167</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5644662976264954</v>
+        <v>0.3784604668617249</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8665569424629211</v>
+        <v>0.7525495290756226</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8996953368186951</v>
+        <v>0.8151466846466064</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>815845</v>
+        <v>204447</v>
       </c>
       <c r="Z4" t="n">
-        <v>11873762</v>
+        <v>2974674</v>
       </c>
       <c r="AA4" t="n">
-        <v>331353</v>
+        <v>83051</v>
       </c>
       <c r="AB4" t="n">
-        <v>21937</v>
+        <v>5499</v>
       </c>
       <c r="AC4" t="n">
-        <v>4580</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>272</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>873860</v>
+        <v>218993</v>
       </c>
       <c r="AG4" t="n">
-        <v>1156298</v>
+        <v>289518</v>
       </c>
       <c r="AH4" t="n">
-        <v>528723</v>
+        <v>132477</v>
       </c>
       <c r="AI4" t="n">
-        <v>120203</v>
+        <v>30129</v>
       </c>
       <c r="AJ4" t="n">
-        <v>199419</v>
+        <v>49913</v>
       </c>
       <c r="AK4" t="n">
-        <v>53016</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571141600608826</v>
+        <v>0.9569721221923828</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910641074180603</v>
+        <v>0.9106499552726746</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578950166702271</v>
+        <v>0.857658863067627</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6622129082679749</v>
+        <v>0.6617317199707031</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018418788909912</v>
+        <v>0.9017962217330933</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313749670982361</v>
+        <v>0.9313249588012695</v>
       </c>
     </row>
     <row r="5">
@@ -1059,152 +1059,152 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>41080</v>
+        <v>18068</v>
       </c>
       <c r="E5" t="n">
-        <v>483180</v>
+        <v>208353</v>
       </c>
       <c r="F5" t="n">
-        <v>3006860</v>
+        <v>617753</v>
       </c>
       <c r="G5" t="n">
-        <v>41336</v>
+        <v>16492</v>
       </c>
       <c r="H5" t="n">
-        <v>147787</v>
+        <v>67041</v>
       </c>
       <c r="I5" t="n">
-        <v>7634</v>
+        <v>4884</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1227973</v>
+        <v>570207</v>
       </c>
       <c r="L5" t="n">
-        <v>1593102</v>
+        <v>729538</v>
       </c>
       <c r="M5" t="n">
-        <v>721017</v>
+        <v>314838</v>
       </c>
       <c r="N5" t="n">
-        <v>181186</v>
+        <v>59402</v>
       </c>
       <c r="O5" t="n">
-        <v>267537</v>
+        <v>127420</v>
       </c>
       <c r="P5" t="n">
-        <v>85379</v>
+        <v>37847</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999935626983643</v>
+        <v>0.9999996423721313</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9618335962295532</v>
+        <v>0.9295771718025208</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9485154747962952</v>
+        <v>0.9062117338180542</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9796745777130127</v>
+        <v>0.9646385908126831</v>
       </c>
       <c r="U5" t="n">
-        <v>0.995860755443573</v>
+        <v>0.9940081834793091</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9916599988937378</v>
+        <v>0.9846176505088806</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9976520538330078</v>
+        <v>0.99568110704422</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>32012</v>
+        <v>8028</v>
       </c>
       <c r="Z5" t="n">
-        <v>339750</v>
+        <v>85185</v>
       </c>
       <c r="AA5" t="n">
-        <v>3197356</v>
+        <v>799643</v>
       </c>
       <c r="AB5" t="n">
-        <v>39755</v>
+        <v>9960</v>
       </c>
       <c r="AC5" t="n">
-        <v>116472</v>
+        <v>29142</v>
       </c>
       <c r="AD5" t="n">
-        <v>2532</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>853179</v>
+        <v>213520</v>
       </c>
       <c r="AG5" t="n">
-        <v>1173987</v>
+        <v>294213</v>
       </c>
       <c r="AH5" t="n">
-        <v>530521</v>
+        <v>132948</v>
       </c>
       <c r="AI5" t="n">
-        <v>120473</v>
+        <v>30191</v>
       </c>
       <c r="AJ5" t="n">
-        <v>200260</v>
+        <v>50113</v>
       </c>
       <c r="AK5" t="n">
-        <v>53099</v>
+        <v>13299</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735596776008606</v>
+        <v>0.9735135436058044</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643242359161377</v>
+        <v>0.9642531871795654</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837833642959595</v>
+        <v>0.9837457537651062</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963153600692749</v>
+        <v>0.9963061213493347</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938810467720032</v>
+        <v>0.9938745498657227</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998375415802002</v>
+        <v>0.9983739256858826</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>27165</v>
+        <v>11381</v>
       </c>
       <c r="E6" t="n">
-        <v>56682</v>
+        <v>18889</v>
       </c>
       <c r="F6" t="n">
-        <v>64240</v>
+        <v>17647</v>
       </c>
       <c r="G6" t="n">
-        <v>175203</v>
+        <v>29789</v>
       </c>
       <c r="H6" t="n">
-        <v>30926</v>
+        <v>10412</v>
       </c>
       <c r="I6" t="n">
-        <v>2146</v>
+        <v>1072</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>25780</v>
+        <v>6462</v>
       </c>
       <c r="Z6" t="n">
-        <v>21382</v>
+        <v>5366</v>
       </c>
       <c r="AA6" t="n">
-        <v>43482</v>
+        <v>10898</v>
       </c>
       <c r="AB6" t="n">
-        <v>235916</v>
+        <v>59000</v>
       </c>
       <c r="AC6" t="n">
-        <v>27905</v>
+        <v>6984</v>
       </c>
       <c r="AD6" t="n">
-        <v>1924</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1263,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>18491</v>
+        <v>12697</v>
       </c>
       <c r="F7" t="n">
-        <v>157072</v>
+        <v>73859</v>
       </c>
       <c r="G7" t="n">
-        <v>35037</v>
+        <v>15077</v>
       </c>
       <c r="H7" t="n">
-        <v>1768777</v>
+        <v>381958</v>
       </c>
       <c r="I7" t="n">
-        <v>56865</v>
+        <v>25765</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3240</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>118437</v>
+        <v>29639</v>
       </c>
       <c r="AB7" t="n">
-        <v>30304</v>
+        <v>7594</v>
       </c>
       <c r="AC7" t="n">
-        <v>1836054</v>
+        <v>459265</v>
       </c>
       <c r="AD7" t="n">
-        <v>48168</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="E8" t="n">
-        <v>948</v>
+        <v>604</v>
       </c>
       <c r="F8" t="n">
-        <v>4030</v>
+        <v>2529</v>
       </c>
       <c r="G8" t="n">
-        <v>1575</v>
+        <v>811</v>
       </c>
       <c r="H8" t="n">
-        <v>78740</v>
+        <v>33867</v>
       </c>
       <c r="I8" t="n">
-        <v>687813</v>
+        <v>155499</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1320</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>1061</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>50282</v>
+        <v>12594</v>
       </c>
       <c r="AD8" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
